--- a/ZonasEscolares/excels/PIURA-SULLANA-SULLANA.xlsx
+++ b/ZonasEscolares/excels/PIURA-SULLANA-SULLANA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PIURA-SULLANA-SULLANA.xlsx
+++ b/ZonasEscolares/excels/PIURA-SULLANA-SULLANA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>502</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-4.89375</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-80.68470000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>367</v>
-      </c>
-      <c r="J2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-4.89375</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-80.6847</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>512 NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-4.89748</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-80.69248</v>
-      </c>
-      <c r="I3" t="n">
-        <v>666</v>
-      </c>
-      <c r="J3" t="n">
-        <v>31</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-4.89748</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-80.69248</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>JOSE EUSEBIO MERINO Y VINCES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-4.90567</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-80.69121</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1656</v>
-      </c>
-      <c r="J4" t="n">
-        <v>82</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-4.90567</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-80.69121</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>516 VIRGEN DEL PERPETUO SOCORRO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-4.90979</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-80.69466</v>
-      </c>
-      <c r="I5" t="n">
-        <v>235</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-4.90979</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-80.69466</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>TENIENTE MIGUEL CORTES</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-4.90303</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-80.69606</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1421</v>
-      </c>
-      <c r="J6" t="n">
-        <v>56</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-4.90303</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-80.69606</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>073 MI SEGUNDO HOGAR</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-4.9037</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-80.6999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>238</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-4.9037</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-80.6999</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>BENJAMIN ZAPATA REYES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-4.90484</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-80.71048999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>227</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-4.90484</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-80.71049</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>503 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-4.90027</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-80.69634000000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>617</v>
-      </c>
-      <c r="J9" t="n">
-        <v>29</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-4.90027</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-80.69634</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>MAYOR PNP (F) ROBERTO VICENTE MORALES ROJAS</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-4.90452</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-80.70177</v>
-      </c>
-      <c r="I10" t="n">
-        <v>667</v>
-      </c>
-      <c r="J10" t="n">
-        <v>34</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-4.90452</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-80.70177</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>530 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-4.91367</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-80.6947</v>
-      </c>
-      <c r="I11" t="n">
-        <v>380</v>
-      </c>
-      <c r="J11" t="n">
-        <v>20</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-4.91367</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-80.6947</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>501 NUESTRA SEÑORA DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-4.91008</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-80.68143000000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>525</v>
-      </c>
-      <c r="J12" t="n">
-        <v>23</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-4.91008</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-80.68143</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>15285-C MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-4.90614</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-80.72172</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1685</v>
-      </c>
-      <c r="J13" t="n">
-        <v>83</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-4.90614</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-80.72172</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1685</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>511 DULCE CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-4.90105</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-80.67793</v>
-      </c>
-      <c r="I14" t="n">
-        <v>429</v>
-      </c>
-      <c r="J14" t="n">
-        <v>18</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-4.90105</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-80.67793</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>517</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-4.90544</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-80.67528</v>
-      </c>
-      <c r="I15" t="n">
-        <v>327</v>
-      </c>
-      <c r="J15" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-4.90544</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-80.67528</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>536 PAUL HARRIS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-4.91177</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-80.68337</v>
-      </c>
-      <c r="I16" t="n">
-        <v>206</v>
-      </c>
-      <c r="J16" t="n">
-        <v>10</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-4.91177</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-80.68337</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>SAN VICENTE DE PIEDRA RODADA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-4.830541</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-80.584069</v>
-      </c>
-      <c r="I17" t="n">
-        <v>822</v>
-      </c>
-      <c r="J17" t="n">
-        <v>36</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-4.830541</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-80.584069</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>14786 FRAY MARTIN DE PORRES / 351 / FRAY MARTIN DE PORRAS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-4.733477</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-80.521377</v>
-      </c>
-      <c r="I18" t="n">
-        <v>690</v>
-      </c>
-      <c r="J18" t="n">
-        <v>36</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-4.733477</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-80.521377</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>14781 HILDEBRANDO CASTRO POZO / 521</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-4.791968</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-80.57382</v>
-      </c>
-      <c r="I19" t="n">
-        <v>849</v>
-      </c>
-      <c r="J19" t="n">
-        <v>50</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-4.791968</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-80.57382</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>15051 JOSE CARLOS MARIATEGUI / JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-4.82434</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-80.41557899999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>393</v>
-      </c>
-      <c r="J20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-4.82434</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-80.415579</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>14787 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-4.89702</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-80.69251</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1398</v>
-      </c>
-      <c r="J21" t="n">
-        <v>61</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-4.89702</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-80.69251</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>15025 JOSE CARDO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-4.89411</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-80.68613999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1659</v>
-      </c>
-      <c r="J22" t="n">
-        <v>70</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-4.89411</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-80.68614</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1659</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>15027 AMAUTA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-4.901218</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-80.691219</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1066</v>
-      </c>
-      <c r="J23" t="n">
-        <v>44</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-4.901218</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-80.691219</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>14778 JOSE M QUINDE TABOADA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-4.91093</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-80.69413</v>
-      </c>
-      <c r="I24" t="n">
-        <v>402</v>
-      </c>
-      <c r="J24" t="n">
-        <v>17</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-4.91093</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-80.69413</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>14785</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-4.90886</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-80.69477999999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>825</v>
-      </c>
-      <c r="J25" t="n">
-        <v>42</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-4.90886</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-80.69478</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>20501 EL NAZARENO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-4.91156</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-80.68713</v>
-      </c>
-      <c r="I26" t="n">
-        <v>403</v>
-      </c>
-      <c r="J26" t="n">
-        <v>11</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-4.91156</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-80.68713</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>15085 JAVIER PEREZ DE CUELLAR</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-4.90398</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-80.71051</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1033</v>
-      </c>
-      <c r="J27" t="n">
-        <v>41</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-4.90398</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-80.71051</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>10406 INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-4.8979</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-80.67663</v>
-      </c>
-      <c r="I28" t="n">
-        <v>279</v>
-      </c>
-      <c r="J28" t="n">
-        <v>16</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-4.8979</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-80.67663</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>14777</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-4.90328</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-80.68626999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>727</v>
-      </c>
-      <c r="J29" t="n">
-        <v>31</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-4.90328</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-80.68627</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>MARIA TERESA OTOYA ARRESE</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-4.90399</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-80.68631999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>396</v>
-      </c>
-      <c r="J30" t="n">
-        <v>22</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-4.90399</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-80.68632</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>ESMELDA JIMENEZ DE VASQUEZ</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-4.9055</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-80.6827</v>
-      </c>
-      <c r="I31" t="n">
-        <v>956</v>
-      </c>
-      <c r="J31" t="n">
-        <v>32</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-4.9055</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-80.6827</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>14790 MARIA IGNACIA GARCIA / 14790 MARIA IGNACIA GARCIA DE GONZALES</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-4.9101</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-80.6844</v>
-      </c>
-      <c r="I32" t="n">
-        <v>534</v>
-      </c>
-      <c r="J32" t="n">
-        <v>30</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-4.9101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-80.6844</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>14789</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-4.89707</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-80.67827</v>
-      </c>
-      <c r="I33" t="n">
-        <v>300</v>
-      </c>
-      <c r="J33" t="n">
-        <v>18</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-4.89707</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-80.67827</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>15029 SANTA TERESA DE JESUS</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-4.901342</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-80.677426</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1027</v>
-      </c>
-      <c r="J34" t="n">
-        <v>42</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-4.901342</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-80.677426</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>20502 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-4.9085</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-80.6751</v>
-      </c>
-      <c r="I35" t="n">
-        <v>499</v>
-      </c>
-      <c r="J35" t="n">
-        <v>31</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-4.9085</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-80.6751</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>20527 AMERICA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-4.90925</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-80.67149000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>910</v>
-      </c>
-      <c r="J36" t="n">
-        <v>41</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-4.90925</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-80.67149</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>10411</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-4.89736</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-80.681867</v>
-      </c>
-      <c r="I37" t="n">
-        <v>605</v>
-      </c>
-      <c r="J37" t="n">
-        <v>34</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-4.89736</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-80.681867</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>CARLOS AUGUSTO SALAVERRY</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-4.89958</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-80.68548</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J38" t="n">
-        <v>106</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-4.89958</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-80.68548</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1671</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>14783</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-4.8942</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-80.685</v>
-      </c>
-      <c r="I39" t="n">
-        <v>463</v>
-      </c>
-      <c r="J39" t="n">
-        <v>21</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-4.8942</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-80.685</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>14107 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-4.824896</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-80.57931499999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>362</v>
-      </c>
-      <c r="J40" t="n">
-        <v>18</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-4.824896</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-80.579315</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>14791</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-4.918255</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-80.64158999999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>569</v>
-      </c>
-      <c r="J41" t="n">
-        <v>49</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-4.918255</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-80.64159</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>GODOFREDO GARCIA BACA</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-4.755435</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-80.51777199999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>502</v>
-      </c>
-      <c r="J42" t="n">
-        <v>30</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-4.755435</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-80.517772</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>15069 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-4.982191</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-80.661384</v>
-      </c>
-      <c r="I43" t="n">
-        <v>428</v>
-      </c>
-      <c r="J43" t="n">
-        <v>27</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-4.982191</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-80.661384</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>15079</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-4.928</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-80.6626</v>
-      </c>
-      <c r="I44" t="n">
-        <v>859</v>
-      </c>
-      <c r="J44" t="n">
-        <v>38</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-4.928</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-80.6626</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>15450 ANTONIO Y MARCOS CAVANIS</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-5.003253</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-80.66593</v>
-      </c>
-      <c r="I45" t="n">
-        <v>572</v>
-      </c>
-      <c r="J45" t="n">
-        <v>40</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-5.003253</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-80.66593</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>MARIO VARGAS LLOSA</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-4.699904</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-80.496236</v>
-      </c>
-      <c r="I46" t="n">
-        <v>530</v>
-      </c>
-      <c r="J46" t="n">
-        <v>32</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-4.699904</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-80.496236</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>JOSE MATIAS MANZANILLA</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-4.893</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-80.6841</v>
-      </c>
-      <c r="I47" t="n">
-        <v>942</v>
-      </c>
-      <c r="J47" t="n">
-        <v>51</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-4.893</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-80.6841</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>INIF 48</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-4.903</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-80.702</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1025</v>
-      </c>
-      <c r="J48" t="n">
-        <v>63</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-4.903</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-80.702</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>EL CUCHO</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-4.868888</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-80.657264</v>
-      </c>
-      <c r="I49" t="n">
-        <v>547</v>
-      </c>
-      <c r="J49" t="n">
-        <v>26</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-4.868888</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-80.657264</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>JORGE BASADRE GROHOMAN</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-4.842112</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-80.596372</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1227</v>
-      </c>
-      <c r="J50" t="n">
-        <v>52</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-4.842112</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-80.596372</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>ADVENTISTA SULLANA</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-4.89571</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-80.6874</v>
-      </c>
-      <c r="I51" t="n">
-        <v>369</v>
-      </c>
-      <c r="J51" t="n">
-        <v>15</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-4.89571</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-80.6874</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-4.90867</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-80.70334</v>
-      </c>
-      <c r="I52" t="n">
-        <v>531</v>
-      </c>
-      <c r="J52" t="n">
-        <v>38</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-4.90867</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-80.70334</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>SAN PEDRO CHANEL</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-4.90886</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-80.70018</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1555</v>
-      </c>
-      <c r="J53" t="n">
-        <v>76</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-4.90886</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-80.70018</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-4.90637</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-80.67666</v>
-      </c>
-      <c r="I54" t="n">
-        <v>484</v>
-      </c>
-      <c r="J54" t="n">
-        <v>28</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-4.90637</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-80.67666</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>SAN JUAN</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-4.893706</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-80.685912</v>
-      </c>
-      <c r="I55" t="n">
-        <v>352</v>
-      </c>
-      <c r="J55" t="n">
-        <v>21</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-4.893706</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-80.685912</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>SANTA ROSA</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-4.8989</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-80.69562999999999</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1312</v>
-      </c>
-      <c r="J56" t="n">
-        <v>68</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-4.8989</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-80.69563</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>DIVINO REDENTOR</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-4.90454</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-80.70883000000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>355</v>
-      </c>
-      <c r="J57" t="n">
-        <v>24</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-4.90454</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-80.70883</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>SAN JOSE OBRERO</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-4.91077</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-80.68171</v>
-      </c>
-      <c r="I58" t="n">
-        <v>893</v>
-      </c>
-      <c r="J58" t="n">
-        <v>40</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-4.91077</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-80.68171</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>FE Y ALEGRIA 18</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-4.9045</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-80.6741</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1512</v>
-      </c>
-      <c r="J59" t="n">
-        <v>74</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-4.9045</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-80.6741</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>14993 SAGRADA FAMILIA / 159 SAGRADA FAMILIA</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-4.954507</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-80.633236</v>
-      </c>
-      <c r="I60" t="n">
-        <v>525</v>
-      </c>
-      <c r="J60" t="n">
-        <v>34</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-4.954507</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-80.633236</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>505 JOSEFA CARDO DE MENA</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-4.88785</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-80.67398</v>
-      </c>
-      <c r="I61" t="n">
-        <v>200</v>
-      </c>
-      <c r="J61" t="n">
-        <v>9</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-4.88785</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-80.67398</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>14793 LUCIANO CASTILLO COLONNA</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-4.88757</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-80.67368999999999</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1420</v>
-      </c>
-      <c r="J62" t="n">
-        <v>78</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-4.88757</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-80.67369</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>COMPLEJO EDUCATIVO SANTA SOFIA</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-4.884967</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-80.840552</v>
-      </c>
-      <c r="I63" t="n">
-        <v>912</v>
-      </c>
-      <c r="J63" t="n">
-        <v>59</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-4.884967</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-80.840552</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>IGNACIO ESCUDERO</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-4.84724</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-80.87301600000001</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1250</v>
-      </c>
-      <c r="J64" t="n">
-        <v>58</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-4.84724</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-80.873016</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>JOSE ILDEFONSO COLOMA</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-4.877546</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-80.70487799999999</v>
-      </c>
-      <c r="I65" t="n">
-        <v>830</v>
-      </c>
-      <c r="J65" t="n">
-        <v>44</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-4.877546</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-80.704878</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>LIZARDO OTERO ALCAS</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-4.9038</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-80.81659999999999</v>
-      </c>
-      <c r="I66" t="n">
-        <v>459</v>
-      </c>
-      <c r="J66" t="n">
-        <v>33</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-4.9038</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-80.8166</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>14277 DIVINO NIÑO</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-4.7805</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-80.58320000000001</v>
-      </c>
-      <c r="I67" t="n">
-        <v>231</v>
-      </c>
-      <c r="J67" t="n">
-        <v>11</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-4.7805</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-80.5832</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>14867 DIVINO SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-4.805498</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-80.635491</v>
-      </c>
-      <c r="I68" t="n">
-        <v>212</v>
-      </c>
-      <c r="J68" t="n">
-        <v>12</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-4.805498</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-80.635491</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>20534 SEÑOR CAUTIVO DE AYABACA</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-4.908524</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-80.724524</v>
-      </c>
-      <c r="I69" t="n">
-        <v>679</v>
-      </c>
-      <c r="J69" t="n">
-        <v>24</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-4.908524</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-80.724524</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-4.839784</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-80.601855</v>
-      </c>
-      <c r="I70" t="n">
-        <v>260</v>
-      </c>
-      <c r="J70" t="n">
-        <v>17</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-4.839784</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-80.601855</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>EXITUS</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-4.8936</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-80.68925</v>
-      </c>
-      <c r="I71" t="n">
-        <v>375</v>
-      </c>
-      <c r="J71" t="n">
-        <v>17</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-4.8936</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-80.68925</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>1137</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-4.90841</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-80.72315</v>
-      </c>
-      <c r="I72" t="n">
-        <v>288</v>
-      </c>
-      <c r="J72" t="n">
-        <v>15</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-4.90841</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-80.72315</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>LAS CAPULLANAS</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-4.8998</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-80.6923</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1939</v>
-      </c>
-      <c r="J73" t="n">
-        <v>74</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-4.8998</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-80.6923</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>DIEGO THOMSON</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-4.90549</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-80.70876</v>
-      </c>
-      <c r="I74" t="n">
-        <v>291</v>
-      </c>
-      <c r="J74" t="n">
-        <v>27</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-4.90549</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-80.70876</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>TALENT SCHOOL SULLANA</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-4.90986</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-80.70113000000001</v>
-      </c>
-      <c r="I75" t="n">
-        <v>250</v>
-      </c>
-      <c r="J75" t="n">
-        <v>27</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-4.90986</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-80.70113</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/PIURA-SULLANA-SULLANA.xlsx
+++ b/ZonasEscolares/excels/PIURA-SULLANA-SULLANA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>434932</t>
+          <t>435026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>BENJAMIN ZAPATA REYES</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-4.89375</t>
+          <t>-4.90484</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.6847</t>
+          <t>-80.71049</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>434951</t>
+          <t>435111</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>512 NUESTRA SEÑORA DE LOURDES</t>
+          <t>536 PAUL HARRIS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-4.89748</t>
+          <t>-4.91177</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.69248</t>
+          <t>-80.68337</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>434970</t>
+          <t>435465</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JOSE EUSEBIO MERINO Y VINCES</t>
+          <t>CARLOS AUGUSTO SALAVERRY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4.90567</t>
+          <t>-4.89958</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.69121</t>
+          <t>-80.68548</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>435007</t>
+          <t>435012</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TENIENTE MIGUEL CORTES</t>
+          <t>073 MI SEGUNDO HOGAR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-4.90303</t>
+          <t>-4.9037</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.69606</t>
+          <t>-80.6999</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,27 +811,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>435012</t>
+          <t>435328</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>073 MI SEGUNDO HOGAR</t>
+          <t>20501 EL NAZARENO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-4.9037</t>
+          <t>-4.91156</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.6999</t>
+          <t>-80.68713</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>403</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>435026</t>
+          <t>437983</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BENJAMIN ZAPATA REYES</t>
+          <t>14277 DIVINO NIÑO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.90484</t>
+          <t>-4.7805</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.71049</t>
+          <t>-80.5832</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>435045</t>
+          <t>438020</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>503 SANTA ROSA DE LIMA</t>
+          <t>14867 DIVINO SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.90027</t>
+          <t>-4.805498</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-80.69634</t>
+          <t>-80.635491</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>435050</t>
+          <t>435106</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MAYOR PNP (F) ROBERTO VICENTE MORALES ROJAS</t>
+          <t>517</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.90452</t>
+          <t>-4.90544</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.70177</t>
+          <t>-80.67528</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>435069</t>
+          <t>435856</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>530 VIRGEN DE LAS MERCEDES</t>
+          <t>ADVENTISTA SULLANA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-4.91367</t>
+          <t>-4.89571</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.6947</t>
+          <t>-80.6874</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>369</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>435074</t>
+          <t>699885</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>501 NUESTRA SEÑORA DE LA MEDALLA MILAGROSA</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.91008</t>
+          <t>-4.90841</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.68143</t>
+          <t>-80.72315</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>435088</t>
+          <t>435352</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15285-C MARIA AUXILIADORA</t>
+          <t>10406 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.90614</t>
+          <t>-4.8979</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.72172</t>
+          <t>-80.67663</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>435093</t>
+          <t>435291</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>511 DULCE CORAZON DE MARIA</t>
+          <t>14778 JOSE M QUINDE TABOADA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.90105</t>
+          <t>-4.91093</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.67793</t>
+          <t>-80.69413</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>402</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>435106</t>
+          <t>552572</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.90544</t>
+          <t>-4.839784</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.67528</t>
+          <t>-80.601855</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>435111</t>
+          <t>583880</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>536 PAUL HARRIS</t>
+          <t>EXITUS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-4.91177</t>
+          <t>-4.8936</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.68337</t>
+          <t>-80.68925</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>435154</t>
+          <t>435093</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE PIEDRA RODADA</t>
+          <t>511 DULCE CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.830541</t>
+          <t>-4.90105</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.584069</t>
+          <t>-80.67793</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>429</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>435205</t>
+          <t>435408</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14786 FRAY MARTIN DE PORRES / 351 / FRAY MARTIN DE PORRAS</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.733477</t>
+          <t>-4.89707</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.521377</t>
+          <t>-80.67827</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>435229</t>
+          <t>435489</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14781 HILDEBRANDO CASTRO POZO / 521</t>
+          <t>14107 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-4.791968</t>
+          <t>-4.824896</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.57382</t>
+          <t>-80.579315</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>435234</t>
+          <t>434932</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15051 JOSE CARLOS MARIATEGUI / JOSE CARLOS MARIATEGUI</t>
+          <t>502</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.82434</t>
+          <t>-4.89375</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.415579</t>
+          <t>-80.6847</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>435253</t>
+          <t>435069</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14787 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>530 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-4.89702</t>
+          <t>-4.91367</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-80.69251</t>
+          <t>-80.6947</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>380</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>435267</t>
+          <t>435470</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15025 JOSE CARDO</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.89411</t>
+          <t>-4.8942</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-80.68614</t>
+          <t>-80.685</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>463</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>435272</t>
+          <t>436064</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>15027 AMAUTA</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.901218</t>
+          <t>-4.893706</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-80.691219</t>
+          <t>-80.685912</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>352</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>435291</t>
+          <t>435371</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14778 JOSE M QUINDE TABOADA</t>
+          <t>MARIA TERESA OTOYA ARRESE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.91093</t>
+          <t>-4.90399</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-80.69413</t>
+          <t>-80.68632</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>435314</t>
+          <t>435074</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>501 NUESTRA SEÑORA DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.90886</t>
+          <t>-4.91008</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-80.69478</t>
+          <t>-80.68143</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>525</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>435328</t>
+          <t>435234</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20501 EL NAZARENO</t>
+          <t>15051 JOSE CARLOS MARIATEGUI / JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.91156</t>
+          <t>-4.82434</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.68713</t>
+          <t>-80.415579</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>393</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>435347</t>
+          <t>436115</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>15085 JAVIER PEREZ DE CUELLAR</t>
+          <t>DIVINO REDENTOR</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.90398</t>
+          <t>-4.90454</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-80.71051</t>
+          <t>-80.70883</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>355</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>435352</t>
+          <t>505241</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10406 INMACULADA CONCEPCION</t>
+          <t>20534 SEÑOR CAUTIVO DE AYABACA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-4.8979</t>
+          <t>-4.908524</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.67663</t>
+          <t>-80.724524</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>679</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>435366</t>
+          <t>435738</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14777</t>
+          <t>EL CUCHO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.90328</t>
+          <t>-4.868888</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-80.68627</t>
+          <t>-80.657264</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>547</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>435371</t>
+          <t>435535</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MARIA TERESA OTOYA ARRESE</t>
+          <t>15069 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-4.90399</t>
+          <t>-4.982191</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-80.68632</t>
+          <t>-80.661384</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>428</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>435385</t>
+          <t>777958</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ESMELDA JIMENEZ DE VASQUEZ</t>
+          <t>DIEGO THOMSON</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.9055</t>
+          <t>-4.90549</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-80.6827</t>
+          <t>-80.70876</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,37 +2361,37 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>435390</t>
+          <t>825285</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14790 MARIA IGNACIA GARCIA / 14790 MARIA IGNACIA GARCIA DE GONZALES</t>
+          <t>TALENT SCHOOL SULLANA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-4.9101</t>
+          <t>-4.90986</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-80.6844</t>
+          <t>-80.70113</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>435408</t>
+          <t>436035</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.89707</t>
+          <t>-4.90637</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-80.67827</t>
+          <t>-80.67666</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>484</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>435413</t>
+          <t>435045</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15029 SANTA TERESA DE JESUS</t>
+          <t>503 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-4.901342</t>
+          <t>-4.90027</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-80.677426</t>
+          <t>-80.69634</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>617</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>435427</t>
+          <t>435390</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20502 NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>14790 MARIA IGNACIA GARCIA / 14790 MARIA IGNACIA GARCIA DE GONZALES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-4.9085</t>
+          <t>-4.9101</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-80.6751</t>
+          <t>-80.6844</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>534</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>435446</t>
+          <t>435521</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20527 AMERICA</t>
+          <t>GODOFREDO GARCIA BACA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.90925</t>
+          <t>-4.755435</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-80.67149</t>
+          <t>-80.517772</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>502</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>435451</t>
+          <t>434951</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>512 NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-4.89736</t>
+          <t>-4.89748</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-80.681867</t>
+          <t>-80.69248</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>666</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>435465</t>
+          <t>435366</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CARLOS AUGUSTO SALAVERRY</t>
+          <t>14777</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-4.89958</t>
+          <t>-4.90328</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-80.68548</t>
+          <t>-80.68627</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>727</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>435470</t>
+          <t>435427</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>20502 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-4.8942</t>
+          <t>-4.9085</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-80.685</t>
+          <t>-80.6751</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>499</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>435489</t>
+          <t>435385</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>14107 SANTA ROSA DE LIMA</t>
+          <t>ESMELDA JIMENEZ DE VASQUEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.824896</t>
+          <t>-4.9055</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-80.579315</t>
+          <t>-80.6827</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>956</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>435494</t>
+          <t>435658</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-4.918255</t>
+          <t>-4.699904</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-80.64159</t>
+          <t>-80.496236</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>530</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>435521</t>
+          <t>437799</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GODOFREDO GARCIA BACA</t>
+          <t>LIZARDO OTERO ALCAS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-4.755435</t>
+          <t>-4.9038</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-80.517772</t>
+          <t>-80.8166</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>459</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>435535</t>
+          <t>435050</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>15069 ALMIRANTE MIGUEL GRAU</t>
+          <t>MAYOR PNP (F) ROBERTO VICENTE MORALES ROJAS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.982191</t>
+          <t>-4.90452</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-80.661384</t>
+          <t>-80.70177</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>667</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>435564</t>
+          <t>435451</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.928</t>
+          <t>-4.89736</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-80.6626</t>
+          <t>-80.681867</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>605</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>435597</t>
+          <t>436219</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>15450 ANTONIO Y MARCOS CAVANIS</t>
+          <t>14993 SAGRADA FAMILIA / 159 SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-5.003253</t>
+          <t>-4.954507</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-80.66593</t>
+          <t>-80.633236</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>525</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>435658</t>
+          <t>435154</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MARIO VARGAS LLOSA</t>
+          <t>SAN VICENTE DE PIEDRA RODADA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-4.699904</t>
+          <t>-4.830541</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-80.496236</t>
+          <t>-80.584069</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>822</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>435719</t>
+          <t>435205</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JOSE MATIAS MANZANILLA</t>
+          <t>14786 FRAY MARTIN DE PORRES / 351 / FRAY MARTIN DE PORRAS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-4.893</t>
+          <t>-4.733477</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-80.6841</t>
+          <t>-80.521377</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>690</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>435724</t>
+          <t>435564</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>INIF 48</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-4.903</t>
+          <t>-4.928</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-80.702</t>
+          <t>-80.6626</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>859</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>435738</t>
+          <t>435998</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>EL CUCHO</t>
+          <t>VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-4.868888</t>
+          <t>-4.90867</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-80.657264</t>
+          <t>-80.70334</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>531</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>435743</t>
+          <t>435597</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JORGE BASADRE GROHOMAN</t>
+          <t>15450 ANTONIO Y MARCOS CAVANIS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-4.842112</t>
+          <t>-5.003253</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-80.596372</t>
+          <t>-80.66593</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>572</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>435856</t>
+          <t>436139</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ADVENTISTA SULLANA</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-4.89571</t>
+          <t>-4.91077</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-80.6874</t>
+          <t>-80.68171</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>893</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>435998</t>
+          <t>435347</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>VIRGEN DEL CARMEN</t>
+          <t>15085 JAVIER PEREZ DE CUELLAR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-4.90867</t>
+          <t>-4.90398</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-80.70334</t>
+          <t>-80.71051</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>436002</t>
+          <t>435446</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SAN PEDRO CHANEL</t>
+          <t>20527 AMERICA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-4.90886</t>
+          <t>-4.90925</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-80.70018</t>
+          <t>-80.67149</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>910</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>436035</t>
+          <t>435314</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>14785</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-4.90637</t>
+          <t>-4.90886</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-80.67666</t>
+          <t>-80.69478</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>825</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>436064</t>
+          <t>435413</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>15029 SANTA TERESA DE JESUS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-4.893706</t>
+          <t>-4.901342</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-80.685912</t>
+          <t>-80.677426</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>436083</t>
+          <t>435272</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>15027 AMAUTA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-4.8989</t>
+          <t>-4.901218</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-80.69563</t>
+          <t>-80.691219</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>436115</t>
+          <t>437596</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>DIVINO REDENTOR</t>
+          <t>JOSE ILDEFONSO COLOMA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-4.90454</t>
+          <t>-4.877546</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-80.70883</t>
+          <t>-80.704878</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>830</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>436139</t>
+          <t>435494</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SAN JOSE OBRERO</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-4.91077</t>
+          <t>-4.918255</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-80.68171</t>
+          <t>-80.64159</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>569</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>436200</t>
+          <t>435229</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 18</t>
+          <t>14781 HILDEBRANDO CASTRO POZO / 521</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-4.9045</t>
+          <t>-4.791968</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-80.6741</t>
+          <t>-80.57382</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>849</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>436219</t>
+          <t>435719</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>14993 SAGRADA FAMILIA / 159 SAGRADA FAMILIA</t>
+          <t>JOSE MATIAS MANZANILLA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-4.954507</t>
+          <t>-4.893</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-80.633236</t>
+          <t>-80.6841</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>942</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>436281</t>
+          <t>435743</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>505 JOSEFA CARDO DE MENA</t>
+          <t>JORGE BASADRE GROHOMAN</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-4.88785</t>
+          <t>-4.842112</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-80.67398</t>
+          <t>-80.596372</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>436304</t>
+          <t>435007</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>14793 LUCIANO CASTILLO COLONNA</t>
+          <t>TENIENTE MIGUEL CORTES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-4.88757</t>
+          <t>-4.90303</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-80.67369</t>
+          <t>-80.69606</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>436455</t>
+          <t>436568</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>COMPLEJO EDUCATIVO SANTA SOFIA</t>
+          <t>IGNACIO ESCUDERO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-4.884967</t>
+          <t>-4.84724</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-80.840552</t>
+          <t>-80.873016</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>436568</t>
+          <t>436455</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>IGNACIO ESCUDERO</t>
+          <t>COMPLEJO EDUCATIVO SANTA SOFIA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-4.84724</t>
+          <t>-4.884967</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-80.873016</t>
+          <t>-80.840552</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>912</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>437596</t>
+          <t>435253</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JOSE ILDEFONSO COLOMA</t>
+          <t>14787 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-4.877546</t>
+          <t>-4.89702</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-80.704878</t>
+          <t>-80.69251</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>437799</t>
+          <t>435724</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LIZARDO OTERO ALCAS</t>
+          <t>INIF 48</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-4.9038</t>
+          <t>-4.903</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-80.8166</t>
+          <t>-80.702</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>437983</t>
+          <t>436083</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>14277 DIVINO NIÑO</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-4.7805</t>
+          <t>-4.8989</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-80.5832</t>
+          <t>-80.69563</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>438020</t>
+          <t>435267</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>14867 DIVINO SEÑOR DE LA MISERICORDIA</t>
+          <t>15025 JOSE CARDO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-4.805498</t>
+          <t>-4.89411</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-80.635491</t>
+          <t>-80.68614</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>505241</t>
+          <t>436200</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20534 SEÑOR CAUTIVO DE AYABACA</t>
+          <t>FE Y ALEGRIA 18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-4.908524</t>
+          <t>-4.9045</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-80.724524</t>
+          <t>-80.6741</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>552572</t>
+          <t>777722</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION</t>
+          <t>LAS CAPULLANAS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-4.839784</t>
+          <t>-4.8998</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-80.601855</t>
+          <t>-80.6923</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>583880</t>
+          <t>436002</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>EXITUS</t>
+          <t>SAN PEDRO CHANEL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-4.8936</t>
+          <t>-4.90886</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-80.68925</t>
+          <t>-80.70018</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>699885</t>
+          <t>436304</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>14793 LUCIANO CASTILLO COLONNA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-4.90841</t>
+          <t>-4.88757</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-80.72315</t>
+          <t>-80.67369</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>777722</t>
+          <t>434970</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LAS CAPULLANAS</t>
+          <t>JOSE EUSEBIO MERINO Y VINCES</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-4.8998</t>
+          <t>-4.90567</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-80.6923</t>
+          <t>-80.69121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>777958</t>
+          <t>435088</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>DIEGO THOMSON</t>
+          <t>15285-C MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-4.90549</t>
+          <t>-4.90614</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-80.70876</t>
+          <t>-80.72172</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>825285</t>
+          <t>436281</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>TALENT SCHOOL SULLANA</t>
+          <t>505 JOSEFA CARDO DE MENA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-4.90986</t>
+          <t>-4.88785</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-80.70113</t>
+          <t>-80.67398</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-SULLANA-SULLANA.xlsx
+++ b/ZonasEscolares/excels/PIURA-SULLANA-SULLANA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>435026</t>
+          <t>825285</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BENJAMIN ZAPATA REYES</t>
+          <t>TALENT SCHOOL SULLANA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-4.90484</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.71049</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-4.90986</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-80.70113</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>435111</t>
+          <t>777958</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>536 PAUL HARRIS</t>
+          <t>DIEGO THOMSON</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-4.91177</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.68337</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-4.90549</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-80.70876</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>435465</t>
+          <t>777722</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CARLOS AUGUSTO SALAVERRY</t>
+          <t>LAS CAPULLANAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4.89958</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.68548</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>-4.8998</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>-80.6923</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>434989</t>
+          <t>699885</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>516 VIRGEN DEL PERPETUO SOCORRO</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-4.90979</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-80.69466</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-4.90841</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-80.72315</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>435012</t>
+          <t>583880</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>073 MI SEGUNDO HOGAR</t>
+          <t>EXITUS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-4.9037</t>
+          <t>375</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.6999</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-4.8936</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-80.68925</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>435328</t>
+          <t>552572</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20501 EL NAZARENO</t>
+          <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-4.91156</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.68713</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-4.839784</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-80.601855</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>437983</t>
+          <t>505241</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14277 DIVINO NIÑO</t>
+          <t>20534 SEÑOR CAUTIVO DE AYABACA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.7805</t>
+          <t>679</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.5832</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-4.908524</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-80.724524</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -945,22 +945,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>-4.805498</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>-80.635491</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>435106</t>
+          <t>437983</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>14277 DIVINO NIÑO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.90544</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.67528</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-4.7805</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-80.5832</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>435856</t>
+          <t>437799</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ADVENTISTA SULLANA</t>
+          <t>LIZARDO OTERO ALCAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-4.89571</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.6874</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>-4.9038</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-80.8166</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>699885</t>
+          <t>437596</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>JOSE ILDEFONSO COLOMA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.90841</t>
+          <t>830</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.72315</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-4.877546</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-80.704878</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>435352</t>
+          <t>436568</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10406 INMACULADA CONCEPCION</t>
+          <t>IGNACIO ESCUDERO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.8979</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.67663</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-4.84724</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-80.873016</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>435291</t>
+          <t>436455</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14778 JOSE M QUINDE TABOADA</t>
+          <t>COMPLEJO EDUCATIVO SANTA SOFIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.91093</t>
+          <t>912</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.69413</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>-4.884967</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-80.840552</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>552572</t>
+          <t>436304</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION</t>
+          <t>14793 LUCIANO CASTILLO COLONNA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.839784</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.601855</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-4.88757</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-80.67369</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>583880</t>
+          <t>436281</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EXITUS</t>
+          <t>505 JOSEFA CARDO DE MENA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-4.8936</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.68925</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>-4.88785</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-80.67398</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>435093</t>
+          <t>436219</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>511 DULCE CORAZON DE MARIA</t>
+          <t>14993 SAGRADA FAMILIA / 159 SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.90105</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.67793</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>-4.954507</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-80.633236</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>435408</t>
+          <t>436200</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>FE Y ALEGRIA 18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.89707</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.67827</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-4.9045</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-80.6741</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>435489</t>
+          <t>436139</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14107 SANTA ROSA DE LIMA</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-4.824896</t>
+          <t>893</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.579315</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-4.91077</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-80.68171</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>434932</t>
+          <t>436115</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>DIVINO REDENTOR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.89375</t>
+          <t>355</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.6847</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-4.90454</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-80.70883</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>435069</t>
+          <t>436083</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>530 VIRGEN DE LAS MERCEDES</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-4.91367</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-80.6947</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>-4.8989</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-80.69563</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>435470</t>
+          <t>436064</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.8942</t>
+          <t>352</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-80.685</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>-4.893706</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.685912</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>436064</t>
+          <t>436035</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.893706</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-80.685912</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>-4.90637</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.67666</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>435371</t>
+          <t>436002</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MARIA TERESA OTOYA ARRESE</t>
+          <t>SAN PEDRO CHANEL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.90399</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-80.68632</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-4.90886</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-80.70018</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>435074</t>
+          <t>435998</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>501 NUESTRA SEÑORA DE LA MEDALLA MILAGROSA</t>
+          <t>VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.91008</t>
+          <t>531</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-80.68143</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>-4.90867</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-80.70334</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>435234</t>
+          <t>435856</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15051 JOSE CARLOS MARIATEGUI / JOSE CARLOS MARIATEGUI</t>
+          <t>ADVENTISTA SULLANA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.82434</t>
+          <t>369</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.415579</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>-4.89571</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-80.6874</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>436115</t>
+          <t>435743</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DIVINO REDENTOR</t>
+          <t>JORGE BASADRE GROHOMAN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.90454</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-80.70883</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>-4.842112</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-80.596372</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>505241</t>
+          <t>435738</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20534 SEÑOR CAUTIVO DE AYABACA</t>
+          <t>EL CUCHO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-4.908524</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.724524</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>-4.868888</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-80.657264</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>435738</t>
+          <t>435724</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EL CUCHO</t>
+          <t>INIF 48</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.868888</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-80.657264</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>-4.903</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-80.702</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>435535</t>
+          <t>435719</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15069 ALMIRANTE MIGUEL GRAU</t>
+          <t>JOSE MATIAS MANZANILLA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-4.982191</t>
+          <t>942</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-80.661384</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>-4.893</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-80.6841</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>777958</t>
+          <t>435658</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DIEGO THOMSON</t>
+          <t>MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.90549</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-80.70876</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-4.699904</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-80.496236</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>825285</t>
+          <t>435597</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TALENT SCHOOL SULLANA</t>
+          <t>15450 ANTONIO Y MARCOS CAVANIS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-4.90986</t>
+          <t>572</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-80.70113</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-5.003253</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-80.66593</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>436035</t>
+          <t>435564</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.90637</t>
+          <t>859</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-80.67666</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>-4.928</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-80.6626</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>435045</t>
+          <t>435535</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>503 SANTA ROSA DE LIMA</t>
+          <t>15069 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-4.90027</t>
+          <t>428</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-80.69634</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>-4.982191</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-80.661384</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>435390</t>
+          <t>435521</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14790 MARIA IGNACIA GARCIA / 14790 MARIA IGNACIA GARCIA DE GONZALES</t>
+          <t>GODOFREDO GARCIA BACA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-4.9101</t>
+          <t>502</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-80.6844</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>-4.755435</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-80.517772</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>435521</t>
+          <t>435494</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GODOFREDO GARCIA BACA</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.755435</t>
+          <t>569</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-80.517772</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>-4.918255</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-80.64159</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>434951</t>
+          <t>435489</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>512 NUESTRA SEÑORA DE LOURDES</t>
+          <t>14107 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-4.89748</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-80.69248</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>-4.824896</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-80.579315</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>435366</t>
+          <t>435470</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>14777</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-4.90328</t>
+          <t>463</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-80.68627</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>-4.8942</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-80.685</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>435427</t>
+          <t>435465</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20502 NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>CARLOS AUGUSTO SALAVERRY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-4.9085</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-80.6751</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>-4.89958</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-80.68548</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>435385</t>
+          <t>435451</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ESMELDA JIMENEZ DE VASQUEZ</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.9055</t>
+          <t>605</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-80.6827</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>-4.89736</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-80.681867</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>435658</t>
+          <t>435446</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MARIO VARGAS LLOSA</t>
+          <t>20527 AMERICA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-4.699904</t>
+          <t>910</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-80.496236</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>-4.90925</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-80.67149</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>437799</t>
+          <t>435427</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LIZARDO OTERO ALCAS</t>
+          <t>20502 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-4.9038</t>
+          <t>499</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-80.8166</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>-4.9085</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-80.6751</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>435050</t>
+          <t>435413</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MAYOR PNP (F) ROBERTO VICENTE MORALES ROJAS</t>
+          <t>15029 SANTA TERESA DE JESUS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.90452</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-80.70177</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>-4.901342</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.677426</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>435451</t>
+          <t>435408</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.89736</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-80.681867</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>-4.89707</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.67827</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>436219</t>
+          <t>435390</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>14993 SAGRADA FAMILIA / 159 SAGRADA FAMILIA</t>
+          <t>14790 MARIA IGNACIA GARCIA / 14790 MARIA IGNACIA GARCIA DE GONZALES</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-4.954507</t>
+          <t>534</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-80.633236</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>-4.9101</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.6844</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>435154</t>
+          <t>435385</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE PIEDRA RODADA</t>
+          <t>ESMELDA JIMENEZ DE VASQUEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-4.830541</t>
+          <t>956</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-80.584069</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>-4.9055</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-80.6827</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>435205</t>
+          <t>435371</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>14786 FRAY MARTIN DE PORRES / 351 / FRAY MARTIN DE PORRAS</t>
+          <t>MARIA TERESA OTOYA ARRESE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-4.733477</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-80.521377</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>-4.90399</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-80.68632</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>435564</t>
+          <t>435366</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>14777</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-4.928</t>
+          <t>727</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-80.6626</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>-4.90328</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-80.68627</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>435998</t>
+          <t>435352</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>VIRGEN DEL CARMEN</t>
+          <t>10406 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-4.90867</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-80.70334</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>-4.8979</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-80.67663</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>435597</t>
+          <t>435347</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>15450 ANTONIO Y MARCOS CAVANIS</t>
+          <t>15085 JAVIER PEREZ DE CUELLAR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-5.003253</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-80.66593</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>-4.90398</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-80.71051</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>436139</t>
+          <t>435328</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SAN JOSE OBRERO</t>
+          <t>20501 EL NAZARENO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-4.91077</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-80.68171</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>-4.91156</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-80.68713</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>435347</t>
+          <t>435314</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>15085 JAVIER PEREZ DE CUELLAR</t>
+          <t>14785</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-4.90398</t>
+          <t>825</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-80.71051</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>-4.90886</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-80.69478</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>435446</t>
+          <t>435291</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20527 AMERICA</t>
+          <t>14778 JOSE M QUINDE TABOADA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-4.90925</t>
+          <t>402</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-80.67149</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>-4.91093</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-80.69413</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>435314</t>
+          <t>435272</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>15027 AMAUTA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-4.90886</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-80.69478</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>-4.901218</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-80.691219</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>435413</t>
+          <t>435267</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>15029 SANTA TERESA DE JESUS</t>
+          <t>15025 JOSE CARDO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-4.901342</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-80.677426</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>-4.89411</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-80.68614</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>435272</t>
+          <t>435253</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>15027 AMAUTA</t>
+          <t>14787 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-4.901218</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-80.691219</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>-4.89702</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-80.69251</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>437596</t>
+          <t>435234</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JOSE ILDEFONSO COLOMA</t>
+          <t>15051 JOSE CARLOS MARIATEGUI / JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-4.877546</t>
+          <t>393</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-80.704878</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>-4.82434</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-80.415579</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>435494</t>
+          <t>435229</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14781 HILDEBRANDO CASTRO POZO / 521</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-4.918255</t>
+          <t>849</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-80.64159</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>-4.791968</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-80.57382</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>435229</t>
+          <t>435205</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>14781 HILDEBRANDO CASTRO POZO / 521</t>
+          <t>14786 FRAY MARTIN DE PORRES / 351 / FRAY MARTIN DE PORRAS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-4.791968</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-80.57382</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>-4.733477</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-80.521377</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>435719</t>
+          <t>435154</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JOSE MATIAS MANZANILLA</t>
+          <t>SAN VICENTE DE PIEDRA RODADA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-4.893</t>
+          <t>822</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-80.6841</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>-4.830541</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-80.584069</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>435743</t>
+          <t>435111</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JORGE BASADRE GROHOMAN</t>
+          <t>536 PAUL HARRIS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-4.842112</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-80.596372</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>-4.91177</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-80.68337</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>435007</t>
+          <t>435106</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TENIENTE MIGUEL CORTES</t>
+          <t>517</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-4.90303</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-80.69606</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>-4.90544</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-80.67528</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>436568</t>
+          <t>435093</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>IGNACIO ESCUDERO</t>
+          <t>511 DULCE CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-4.84724</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-80.873016</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>-4.90105</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-80.67793</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>436455</t>
+          <t>435088</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>COMPLEJO EDUCATIVO SANTA SOFIA</t>
+          <t>15285-C MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-4.884967</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-80.840552</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>-4.90614</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-80.72172</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>435253</t>
+          <t>435074</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>14787 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>501 NUESTRA SEÑORA DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-4.89702</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-80.69251</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>-4.91008</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-80.68143</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>435724</t>
+          <t>435069</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>INIF 48</t>
+          <t>530 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-4.903</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-80.702</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>-4.91367</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-80.6947</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,37 +4531,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>436083</t>
+          <t>435050</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>MAYOR PNP (F) ROBERTO VICENTE MORALES ROJAS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-4.8989</t>
+          <t>667</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-80.69563</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>-4.90452</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-80.70177</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>435267</t>
+          <t>435045</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>15025 JOSE CARDO</t>
+          <t>503 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-4.89411</t>
+          <t>617</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-80.68614</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>-4.90027</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-80.69634</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>436200</t>
+          <t>435026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 18</t>
+          <t>BENJAMIN ZAPATA REYES</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-4.9045</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-80.6741</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>-4.90484</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-80.71049</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>777722</t>
+          <t>435012</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>LAS CAPULLANAS</t>
+          <t>073 MI SEGUNDO HOGAR</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-4.8998</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-80.6923</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>-4.9037</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-80.6999</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>436002</t>
+          <t>435007</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SAN PEDRO CHANEL</t>
+          <t>TENIENTE MIGUEL CORTES</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-4.90886</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-80.70018</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>-4.90303</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-80.69606</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>436304</t>
+          <t>434989</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>14793 LUCIANO CASTILLO COLONNA</t>
+          <t>516 VIRGEN DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-4.88757</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-80.67369</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>-4.90979</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-80.69466</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4913,22 +4913,22 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
           <t>-4.90567</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>-80.69121</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1656</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>82</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>435088</t>
+          <t>434951</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>15285-C MARIA AUXILIADORA</t>
+          <t>512 NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-4.90614</t>
+          <t>666</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-80.72172</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>-4.89748</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-80.69248</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>436281</t>
+          <t>434932</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>505 JOSEFA CARDO DE MENA</t>
+          <t>502</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-4.88785</t>
+          <t>367</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-80.67398</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-4.89375</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-80.6847</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-SULLANA-SULLANA.xlsx
+++ b/ZonasEscolares/excels/PIURA-SULLANA-SULLANA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
